--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>98404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R2" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B3" t="n">
-        <v>98402</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R3" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B2" t="n">
-        <v>98404</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R2" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>98410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R3" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419452</v>
       </c>
       <c r="B2" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419449</v>
       </c>
       <c r="B3" t="n">
-        <v>98410</v>
+        <v>98413</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>98430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R2" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B3" t="n">
-        <v>98413</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R3" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B2" t="n">
-        <v>98430</v>
+        <v>90988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R2" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>98536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R3" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B2" t="n">
-        <v>90988</v>
+        <v>98538</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R2" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R3" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419449</v>
       </c>
       <c r="B2" t="n">
-        <v>98538</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R2" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R3" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 33614-2023 artfynd.xlsx
+++ b/artfynd/A 33614-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419452</v>
+        <v>123419449</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602183</v>
+        <v>602188</v>
       </c>
       <c r="R2" t="n">
-        <v>6887924</v>
+        <v>6887912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2189</t>
+          <t>2024_2191</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419449</v>
+        <v>123419452</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602188</v>
+        <v>602183</v>
       </c>
       <c r="R3" t="n">
-        <v>6887912</v>
+        <v>6887924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2191</t>
+          <t>2024_2189</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
